--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
@@ -441,7 +441,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>934.52</v>
+        <v>934.23</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -450,7 +450,7 @@
         <v>39234.21</v>
       </c>
       <c r="F2">
-        <v>1244.7</v>
+        <v>1243.02</v>
       </c>
       <c r="G2">
         <v>329.01</v>
@@ -459,25 +459,25 @@
         <v>664.61</v>
       </c>
       <c r="I2">
-        <v>1196.44</v>
+        <v>1196.43</v>
       </c>
       <c r="J2">
         <v>23106</v>
       </c>
       <c r="K2">
-        <v>21593119.8</v>
+        <v>21586307.96</v>
       </c>
       <c r="L2">
-        <v>934.52</v>
+        <v>934.23</v>
       </c>
       <c r="M2">
-        <v>8.19</v>
+        <v>8.18</v>
       </c>
       <c r="N2">
-        <v>918.47</v>
+        <v>918.2</v>
       </c>
       <c r="O2">
-        <v>950.5700000000001</v>
+        <v>950.26</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>431.12</v>
+        <v>266.75</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -499,34 +499,34 @@
         <v>40257.84</v>
       </c>
       <c r="F3">
-        <v>925.28</v>
+        <v>757.33</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>164.32</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>549.24</v>
+        <v>239.64</v>
       </c>
       <c r="J3">
-        <v>14300</v>
+        <v>23106</v>
       </c>
       <c r="K3">
-        <v>6164987.9</v>
+        <v>6163636.57</v>
       </c>
       <c r="L3">
-        <v>266.81</v>
+        <v>266.75</v>
       </c>
       <c r="M3">
-        <v>7.74</v>
+        <v>4.98</v>
       </c>
       <c r="N3">
-        <v>415.95</v>
+        <v>256.99</v>
       </c>
       <c r="O3">
-        <v>446.28</v>
+        <v>276.52</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1043.6</v>
+        <v>1043.27</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -548,10 +548,10 @@
         <v>39234.21</v>
       </c>
       <c r="F4">
-        <v>1271.32</v>
+        <v>1269.53</v>
       </c>
       <c r="G4">
-        <v>378.34</v>
+        <v>377.82</v>
       </c>
       <c r="H4">
         <v>732.89</v>
@@ -563,19 +563,19 @@
         <v>20691</v>
       </c>
       <c r="K4">
-        <v>21593119.8</v>
+        <v>21586307.96</v>
       </c>
       <c r="L4">
-        <v>1043.6</v>
+        <v>1043.27</v>
       </c>
       <c r="M4">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
       <c r="N4">
-        <v>1026.28</v>
+        <v>1025.97</v>
       </c>
       <c r="O4">
-        <v>1060.92</v>
+        <v>1060.57</v>
       </c>
     </row>
     <row r="5">
@@ -588,7 +588,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>461.45</v>
+        <v>297.89</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -597,34 +597,34 @@
         <v>40257.84</v>
       </c>
       <c r="F5">
-        <v>949.9400000000001</v>
+        <v>794.5</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>179.56</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>595.37</v>
+        <v>328.63</v>
       </c>
       <c r="J5">
-        <v>13360</v>
+        <v>20691</v>
       </c>
       <c r="K5">
-        <v>6164987.9</v>
+        <v>6163636.57</v>
       </c>
       <c r="L5">
-        <v>297.96</v>
+        <v>297.89</v>
       </c>
       <c r="M5">
-        <v>8.220000000000001</v>
+        <v>5.52</v>
       </c>
       <c r="N5">
-        <v>445.34</v>
+        <v>287.06</v>
       </c>
       <c r="O5">
-        <v>477.56</v>
+        <v>308.72</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
@@ -441,43 +441,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>934.23</v>
+        <v>957.64</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>39234.21</v>
+        <v>30732.06</v>
       </c>
       <c r="F2">
-        <v>1243.02</v>
+        <v>1232.6</v>
       </c>
       <c r="G2">
-        <v>329.01</v>
+        <v>328.95</v>
       </c>
       <c r="H2">
-        <v>664.61</v>
+        <v>683.62</v>
       </c>
       <c r="I2">
-        <v>1196.43</v>
+        <v>1229.42</v>
       </c>
       <c r="J2">
         <v>23106</v>
       </c>
       <c r="K2">
-        <v>21586307.96</v>
+        <v>22127181</v>
       </c>
       <c r="L2">
-        <v>934.23</v>
+        <v>957.64</v>
       </c>
       <c r="M2">
-        <v>8.18</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N2">
-        <v>918.2</v>
+        <v>941.74</v>
       </c>
       <c r="O2">
-        <v>950.26</v>
+        <v>973.53</v>
       </c>
     </row>
     <row r="3">
@@ -490,43 +490,43 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>266.75</v>
+        <v>441.79</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>40257.84</v>
+        <v>29078.34</v>
       </c>
       <c r="F3">
-        <v>757.33</v>
+        <v>898.51</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>164.48</v>
       </c>
       <c r="I3">
-        <v>239.64</v>
+        <v>568.1</v>
       </c>
       <c r="J3">
-        <v>23106</v>
+        <v>14300</v>
       </c>
       <c r="K3">
-        <v>6163636.57</v>
+        <v>6317653.79</v>
       </c>
       <c r="L3">
-        <v>266.75</v>
+        <v>273.42</v>
       </c>
       <c r="M3">
-        <v>4.98</v>
+        <v>7.51</v>
       </c>
       <c r="N3">
-        <v>256.99</v>
+        <v>427.07</v>
       </c>
       <c r="O3">
-        <v>276.52</v>
+        <v>456.52</v>
       </c>
     </row>
     <row r="4">
@@ -539,43 +539,43 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1043.27</v>
+        <v>1069.41</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>39234.21</v>
+        <v>30732.06</v>
       </c>
       <c r="F4">
-        <v>1269.53</v>
+        <v>1255.82</v>
       </c>
       <c r="G4">
-        <v>377.82</v>
+        <v>389.34</v>
       </c>
       <c r="H4">
-        <v>732.89</v>
+        <v>755.89</v>
       </c>
       <c r="I4">
-        <v>1292.49</v>
+        <v>1327.79</v>
       </c>
       <c r="J4">
         <v>20691</v>
       </c>
       <c r="K4">
-        <v>21586307.96</v>
+        <v>22127181</v>
       </c>
       <c r="L4">
-        <v>1043.27</v>
+        <v>1069.41</v>
       </c>
       <c r="M4">
-        <v>8.83</v>
+        <v>8.73</v>
       </c>
       <c r="N4">
-        <v>1025.97</v>
+        <v>1052.3</v>
       </c>
       <c r="O4">
-        <v>1060.57</v>
+        <v>1086.52</v>
       </c>
     </row>
     <row r="5">
@@ -588,43 +588,43 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>297.89</v>
+        <v>472.88</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>40257.84</v>
+        <v>29078.34</v>
       </c>
       <c r="F5">
-        <v>794.5</v>
+        <v>921.64</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>181.16</v>
       </c>
       <c r="I5">
-        <v>328.63</v>
+        <v>614.28</v>
       </c>
       <c r="J5">
-        <v>20691</v>
+        <v>13360</v>
       </c>
       <c r="K5">
-        <v>6163636.57</v>
+        <v>6317653.79</v>
       </c>
       <c r="L5">
-        <v>297.89</v>
+        <v>305.33</v>
       </c>
       <c r="M5">
-        <v>5.52</v>
+        <v>7.97</v>
       </c>
       <c r="N5">
-        <v>287.06</v>
+        <v>457.25</v>
       </c>
       <c r="O5">
-        <v>308.72</v>
+        <v>488.51</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
@@ -441,43 +441,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>957.64</v>
+        <v>966.03</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>30732.06</v>
+        <v>32623.33</v>
       </c>
       <c r="F2">
-        <v>1232.6</v>
+        <v>1266.19</v>
       </c>
       <c r="G2">
-        <v>328.95</v>
+        <v>268.17</v>
       </c>
       <c r="H2">
-        <v>683.62</v>
+        <v>623.0700000000001</v>
       </c>
       <c r="I2">
-        <v>1229.42</v>
+        <v>1248.48</v>
       </c>
       <c r="J2">
         <v>23106</v>
       </c>
       <c r="K2">
-        <v>22127181</v>
+        <v>22321112.68</v>
       </c>
       <c r="L2">
-        <v>957.64</v>
+        <v>966.03</v>
       </c>
       <c r="M2">
-        <v>8.109999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="N2">
-        <v>941.74</v>
+        <v>949.7</v>
       </c>
       <c r="O2">
-        <v>973.53</v>
+        <v>982.36</v>
       </c>
     </row>
     <row r="3">
@@ -490,43 +490,43 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>441.79</v>
+        <v>425.09</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>29078.34</v>
+        <v>21031.5</v>
       </c>
       <c r="F3">
-        <v>898.51</v>
+        <v>865.1799999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>164.48</v>
+        <v>133.58</v>
       </c>
       <c r="I3">
-        <v>568.1</v>
+        <v>524.78</v>
       </c>
       <c r="J3">
         <v>14300</v>
       </c>
       <c r="K3">
-        <v>6317653.79</v>
+        <v>6078830.07</v>
       </c>
       <c r="L3">
-        <v>273.42</v>
+        <v>263.08</v>
       </c>
       <c r="M3">
-        <v>7.51</v>
+        <v>7.24</v>
       </c>
       <c r="N3">
-        <v>427.07</v>
+        <v>410.91</v>
       </c>
       <c r="O3">
-        <v>456.52</v>
+        <v>439.27</v>
       </c>
     </row>
     <row r="4">
@@ -539,43 +539,43 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1069.41</v>
+        <v>1078.78</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>30732.06</v>
+        <v>32623.33</v>
       </c>
       <c r="F4">
-        <v>1255.82</v>
+        <v>1291.79</v>
       </c>
       <c r="G4">
-        <v>389.34</v>
+        <v>360.31</v>
       </c>
       <c r="H4">
-        <v>755.89</v>
+        <v>719.65</v>
       </c>
       <c r="I4">
-        <v>1327.79</v>
+        <v>1357.87</v>
       </c>
       <c r="J4">
         <v>20691</v>
       </c>
       <c r="K4">
-        <v>22127181</v>
+        <v>22321112.68</v>
       </c>
       <c r="L4">
-        <v>1069.41</v>
+        <v>1078.78</v>
       </c>
       <c r="M4">
-        <v>8.73</v>
+        <v>8.98</v>
       </c>
       <c r="N4">
-        <v>1052.3</v>
+        <v>1061.18</v>
       </c>
       <c r="O4">
-        <v>1086.52</v>
+        <v>1096.39</v>
       </c>
     </row>
     <row r="5">
@@ -588,43 +588,43 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>472.88</v>
+        <v>455</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>29078.34</v>
+        <v>21031.5</v>
       </c>
       <c r="F5">
-        <v>921.64</v>
+        <v>887.47</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>181.16</v>
+        <v>164.48</v>
       </c>
       <c r="I5">
-        <v>614.28</v>
+        <v>565.9400000000001</v>
       </c>
       <c r="J5">
         <v>13360</v>
       </c>
       <c r="K5">
-        <v>6317653.79</v>
+        <v>6078830.07</v>
       </c>
       <c r="L5">
-        <v>305.33</v>
+        <v>293.79</v>
       </c>
       <c r="M5">
-        <v>7.97</v>
+        <v>7.68</v>
       </c>
       <c r="N5">
-        <v>457.25</v>
+        <v>439.95</v>
       </c>
       <c r="O5">
-        <v>488.51</v>
+        <v>470.05</v>
       </c>
     </row>
   </sheetData>
